--- a/Модель_покрытия_2026_для_заполнения_1.xlsx
+++ b/Модель_покрытия_2026_для_заполнения_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FD636B-78E2-41A4-8081-87D5FCA0D677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C739485-172E-443C-A7B4-309AB87C28BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{557A26C6-F21E-4F13-8F97-2AB80881C4B7}"/>
   </bookViews>
@@ -2825,7 +2825,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3468" uniqueCount="407">
   <si>
     <t>DL 11.02</t>
   </si>
@@ -4055,21 +4055,6 @@
   </si>
   <si>
     <t>Продажи Magnit (SO) l</t>
-  </si>
-  <si>
-    <t>RKADM итог</t>
-  </si>
-  <si>
-    <t>Skyline итог</t>
-  </si>
-  <si>
-    <t>не Skyline итог</t>
-  </si>
-  <si>
-    <t>execution</t>
-  </si>
-  <si>
-    <t>лидирование</t>
   </si>
   <si>
     <t>RKADM avg</t>
@@ -8683,7 +8668,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEBB7BC1-AB84-4C97-A7A0-E851126C3CB4}">
-  <dimension ref="A1:AK194"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AK193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="262" customWidth="1"/>
@@ -8897,22 +8883,22 @@
         <v>143</v>
       </c>
       <c r="AF3" s="315" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AG3" s="315" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="AH3" s="315" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AI3" s="315" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AJ3" s="315" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="F4" s="263"/>
       <c r="G4" s="263"/>
       <c r="I4" s="264"/>
@@ -8954,7 +8940,7 @@
         <v>2220726460.6154871</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="262" t="s">
         <v>149</v>
       </c>
@@ -9012,7 +8998,7 @@
         <v>271516.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="262" t="s">
         <v>152</v>
       </c>
@@ -9055,7 +9041,7 @@
       <c r="Y6" s="266"/>
       <c r="AE6" s="267"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="262" t="s">
         <v>149</v>
       </c>
@@ -9179,7 +9165,7 @@
         <v>21870426.049999997</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="262" t="s">
         <v>160</v>
       </c>
@@ -9231,7 +9217,7 @@
         <v>1288855.8400000001</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="262" t="s">
         <v>152</v>
       </c>
@@ -9276,7 +9262,7 @@
       <c r="AC10" s="267"/>
       <c r="AE10" s="267"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="262" t="s">
         <v>164</v>
       </c>
@@ -9326,7 +9312,7 @@
       </c>
       <c r="AE11" s="267"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="262" t="s">
         <v>165</v>
       </c>
@@ -9376,7 +9362,7 @@
       </c>
       <c r="AE12" s="267"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="262" t="s">
         <v>168</v>
       </c>
@@ -9421,7 +9407,7 @@
       </c>
       <c r="AE13" s="267"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="262" t="s">
         <v>168</v>
       </c>
@@ -9468,7 +9454,7 @@
       </c>
       <c r="AE14" s="267"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="262" t="s">
         <v>171</v>
       </c>
@@ -9518,7 +9504,7 @@
       </c>
       <c r="AE15" s="267"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="262" t="s">
         <v>173</v>
       </c>
@@ -9565,7 +9551,7 @@
       <c r="AC16" s="267"/>
       <c r="AE16" s="267"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="262" t="s">
         <v>174</v>
       </c>
@@ -9614,7 +9600,7 @@
       </c>
       <c r="AE17" s="267"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="262" t="s">
         <v>160</v>
       </c>
@@ -9661,7 +9647,7 @@
       <c r="AC18" s="267"/>
       <c r="AE18" s="267"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="262" t="s">
         <v>176</v>
       </c>
@@ -9711,7 +9697,7 @@
       </c>
       <c r="AE19" s="267"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="262" t="s">
         <v>149</v>
       </c>
@@ -9782,7 +9768,7 @@
         <v>1997857.99</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="262" t="s">
         <v>176</v>
       </c>
@@ -9838,7 +9824,7 @@
         <v>16290350.629999997</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="262" t="s">
         <v>171</v>
       </c>
@@ -9929,7 +9915,7 @@
       <c r="X23" s="218"/>
       <c r="AE23" s="267"/>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="262" t="s">
         <v>174</v>
       </c>
@@ -9978,7 +9964,7 @@
         <v>6582960</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="262" t="s">
         <v>174</v>
       </c>
@@ -10013,7 +9999,7 @@
         <v>293012.60000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="262" t="s">
         <v>168</v>
       </c>
@@ -10059,7 +10045,7 @@
         <v>63038286.849999949</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="262" t="s">
         <v>168</v>
       </c>
@@ -10159,7 +10145,7 @@
       <c r="W28" s="267"/>
       <c r="AE28" s="267"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="262" t="s">
         <v>168</v>
       </c>
@@ -10239,7 +10225,7 @@
       <c r="W30" s="267"/>
       <c r="AE30" s="267"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="262" t="s">
         <v>164</v>
       </c>
@@ -10280,7 +10266,7 @@
       <c r="W31" s="267"/>
       <c r="AE31" s="267"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="262" t="s">
         <v>164</v>
       </c>
@@ -10408,7 +10394,7 @@
       <c r="S34" s="265"/>
       <c r="AE34" s="267"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="262" t="s">
         <v>156</v>
       </c>
@@ -10441,7 +10427,7 @@
       <c r="S35" s="265"/>
       <c r="AE35" s="267"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="262" t="s">
         <v>173</v>
       </c>
@@ -10492,7 +10478,7 @@
         <v>669466</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="262" t="s">
         <v>173</v>
       </c>
@@ -10596,7 +10582,7 @@
       </c>
       <c r="AE38" s="267"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="262" t="s">
         <v>165</v>
       </c>
@@ -10629,7 +10615,7 @@
       <c r="S39" s="265"/>
       <c r="AE39" s="267"/>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="262" t="s">
         <v>165</v>
       </c>
@@ -10725,7 +10711,7 @@
       <c r="S41" s="265"/>
       <c r="AE41" s="267"/>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="262" t="s">
         <v>165</v>
       </c>
@@ -10824,7 +10810,7 @@
         <v>3859752.72</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="262" t="s">
         <v>192</v>
       </c>
@@ -10847,7 +10833,7 @@
       </c>
       <c r="J44" s="267"/>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="262" t="s">
         <v>192</v>
       </c>
@@ -10890,7 +10876,7 @@
       <c r="AC45" s="272"/>
       <c r="AD45" s="272"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="262" t="s">
         <v>192</v>
       </c>
@@ -10912,7 +10898,7 @@
         <v>228590.15</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="262" t="s">
         <v>192</v>
       </c>
@@ -10935,7 +10921,7 @@
       </c>
       <c r="X47" s="273"/>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="262" t="s">
         <v>195</v>
       </c>
@@ -10957,7 +10943,7 @@
         <v>44163988.919999994</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="281" t="s">
         <v>195</v>
       </c>
@@ -10997,7 +10983,7 @@
       <c r="AC49" s="274"/>
       <c r="AD49" s="274"/>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="262" t="s">
         <v>196</v>
       </c>
@@ -11037,7 +11023,7 @@
       <c r="AC50" s="265"/>
       <c r="AD50" s="265"/>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="281" t="s">
         <v>196</v>
       </c>
@@ -11080,7 +11066,7 @@
       <c r="AC51" s="265"/>
       <c r="AD51" s="265"/>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="262" t="s">
         <v>197</v>
       </c>
@@ -11123,7 +11109,7 @@
       <c r="AC52" s="265"/>
       <c r="AD52" s="265"/>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="281" t="s">
         <v>197</v>
       </c>
@@ -11166,7 +11152,7 @@
       <c r="AC53" s="265"/>
       <c r="AD53" s="265"/>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="281" t="s">
         <v>198</v>
       </c>
@@ -11209,7 +11195,7 @@
       <c r="AC54" s="265"/>
       <c r="AD54" s="265"/>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="262" t="s">
         <v>200</v>
       </c>
@@ -11252,7 +11238,7 @@
       <c r="AC55" s="265"/>
       <c r="AD55" s="265"/>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="281" t="s">
         <v>200</v>
       </c>
@@ -11295,7 +11281,7 @@
       <c r="AC56" s="265"/>
       <c r="AD56" s="265"/>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="281" t="s">
         <v>203</v>
       </c>
@@ -11338,7 +11324,7 @@
       <c r="AC57" s="265"/>
       <c r="AD57" s="265"/>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="281" t="s">
         <v>176</v>
       </c>
@@ -11381,7 +11367,7 @@
       <c r="AC58" s="265"/>
       <c r="AD58" s="265"/>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="281" t="s">
         <v>204</v>
       </c>
@@ -11424,7 +11410,7 @@
       <c r="AC59" s="265"/>
       <c r="AD59" s="265"/>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="281" t="s">
         <v>205</v>
       </c>
@@ -11467,7 +11453,7 @@
       <c r="AC60" s="265"/>
       <c r="AD60" s="265"/>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="281" t="s">
         <v>206</v>
       </c>
@@ -11510,7 +11496,7 @@
       <c r="AC61" s="265"/>
       <c r="AD61" s="265"/>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="281" t="s">
         <v>208</v>
       </c>
@@ -11553,7 +11539,7 @@
       <c r="AC62" s="265"/>
       <c r="AD62" s="265"/>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="262" t="s">
         <v>209</v>
       </c>
@@ -11596,7 +11582,7 @@
       <c r="AC63" s="265"/>
       <c r="AD63" s="265"/>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="281" t="s">
         <v>209</v>
       </c>
@@ -11639,7 +11625,7 @@
       <c r="AC64" s="265"/>
       <c r="AD64" s="265"/>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="281" t="s">
         <v>210</v>
       </c>
@@ -11682,7 +11668,7 @@
       <c r="AC65" s="265"/>
       <c r="AD65" s="265"/>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="313" t="s">
         <v>211</v>
       </c>
@@ -11725,7 +11711,7 @@
       <c r="AC66" s="265"/>
       <c r="AD66" s="265"/>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="281" t="s">
         <v>212</v>
       </c>
@@ -11770,7 +11756,7 @@
       <c r="AD67" s="276"/>
       <c r="AE67" s="276"/>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="281" t="s">
         <v>214</v>
       </c>
@@ -11813,7 +11799,7 @@
       <c r="AC68" s="265"/>
       <c r="AD68" s="265"/>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="281" t="s">
         <v>215</v>
       </c>
@@ -11856,7 +11842,7 @@
       <c r="AC69" s="265"/>
       <c r="AD69" s="265"/>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="281" t="s">
         <v>216</v>
       </c>
@@ -11899,7 +11885,7 @@
       <c r="AC70" s="265"/>
       <c r="AD70" s="265"/>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="281" t="s">
         <v>217</v>
       </c>
@@ -11921,7 +11907,7 @@
         <v>3642683.080000001</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="313" t="s">
         <v>219</v>
       </c>
@@ -11943,7 +11929,7 @@
         <v>16476732.709999997</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="281" t="s">
         <v>221</v>
       </c>
@@ -11965,7 +11951,7 @@
         <v>1067159.2200000002</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="281" t="s">
         <v>222</v>
       </c>
@@ -12008,7 +11994,7 @@
       <c r="AC74" s="272"/>
       <c r="AD74" s="272"/>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="281" t="s">
         <v>224</v>
       </c>
@@ -12030,7 +12016,7 @@
         <v>217936.43</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="262" t="s">
         <v>225</v>
       </c>
@@ -12052,7 +12038,7 @@
         <v>18206006.04000001</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="281" t="s">
         <v>225</v>
       </c>
@@ -12074,7 +12060,7 @@
         <v>22305574.450000003</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="281" t="s">
         <v>226</v>
       </c>
@@ -12096,7 +12082,7 @@
         <v>148303293.16999984</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="281" t="s">
         <v>144</v>
       </c>
@@ -12118,7 +12104,7 @@
         <v>18010939.100000005</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="281" t="s">
         <v>227</v>
       </c>
@@ -12140,7 +12126,7 @@
         <v>8843623.5500000007</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="281" t="s">
         <v>228</v>
       </c>
@@ -12162,7 +12148,7 @@
         <v>4388912.41</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="281" t="s">
         <v>229</v>
       </c>
@@ -12184,7 +12170,7 @@
         <v>16865038.440000001</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="281" t="s">
         <v>230</v>
       </c>
@@ -12206,7 +12192,7 @@
         <v>2126298.59</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="281" t="s">
         <v>231</v>
       </c>
@@ -12228,7 +12214,7 @@
         <v>2711752.3</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="262" t="s">
         <v>232</v>
       </c>
@@ -12250,7 +12236,7 @@
         <v>6187042.1399999997</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="281" t="s">
         <v>232</v>
       </c>
@@ -12272,7 +12258,7 @@
         <v>6168560.4500000011</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="281" t="s">
         <v>233</v>
       </c>
@@ -12294,7 +12280,7 @@
         <v>13379034.709999999</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="281" t="s">
         <v>149</v>
       </c>
@@ -12316,7 +12302,7 @@
         <v>2367448.2399999998</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="281" t="s">
         <v>235</v>
       </c>
@@ -12338,7 +12324,7 @@
         <v>66978.100000000006</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="281" t="s">
         <v>236</v>
       </c>
@@ -12360,7 +12346,7 @@
         <v>1620898.1300000001</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="281" t="s">
         <v>171</v>
       </c>
@@ -12382,7 +12368,7 @@
         <v>36021878.200000018</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="281" t="s">
         <v>237</v>
       </c>
@@ -12404,7 +12390,7 @@
         <v>132631.12</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="281" t="s">
         <v>238</v>
       </c>
@@ -12426,7 +12412,7 @@
         <v>7241718.1199999992</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="281" t="s">
         <v>239</v>
       </c>
@@ -12448,7 +12434,7 @@
         <v>2537846.2700000005</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="281" t="s">
         <v>241</v>
       </c>
@@ -12470,7 +12456,7 @@
         <v>1761030.05</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="281" t="s">
         <v>174</v>
       </c>
@@ -12492,7 +12478,7 @@
         <v>6875972.790000001</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="281" t="s">
         <v>242</v>
       </c>
@@ -12514,7 +12500,7 @@
         <v>166482.5</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="281" t="s">
         <v>243</v>
       </c>
@@ -12536,7 +12522,7 @@
         <v>923748.45000000019</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="281" t="s">
         <v>244</v>
       </c>
@@ -12558,7 +12544,7 @@
         <v>915171.79</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="281" t="s">
         <v>245</v>
       </c>
@@ -12580,7 +12566,7 @@
         <v>24173379.469999999</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="281" t="s">
         <v>246</v>
       </c>
@@ -12602,7 +12588,7 @@
         <v>3460921.04</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="281" t="s">
         <v>247</v>
       </c>
@@ -12624,7 +12610,7 @@
         <v>3728265.5200000005</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="281" t="s">
         <v>164</v>
       </c>
@@ -12646,7 +12632,7 @@
         <v>292274.43</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="281" t="s">
         <v>248</v>
       </c>
@@ -12668,7 +12654,7 @@
         <v>372200.5</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="281" t="s">
         <v>185</v>
       </c>
@@ -12690,7 +12676,7 @@
         <v>5559329.3000000007</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="281" t="s">
         <v>249</v>
       </c>
@@ -12712,7 +12698,7 @@
         <v>1871079.9999999998</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="281" t="s">
         <v>156</v>
       </c>
@@ -12734,7 +12720,7 @@
         <v>21870426.050000016</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="281" t="s">
         <v>173</v>
       </c>
@@ -12756,7 +12742,7 @@
         <v>669465.87</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="281" t="s">
         <v>165</v>
       </c>
@@ -12778,7 +12764,7 @@
         <v>59178799.899999708</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="313" t="s">
         <v>250</v>
       </c>
@@ -12800,7 +12786,7 @@
         <v>221696.62000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="281" t="s">
         <v>191</v>
       </c>
@@ -12822,7 +12808,7 @@
         <v>3859752.7199999997</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="281" t="s">
         <v>251</v>
       </c>
@@ -12844,7 +12830,7 @@
         <v>1319912.0300000003</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="262" t="s">
         <v>252</v>
       </c>
@@ -12866,7 +12852,7 @@
         <v>18991406.05999998</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="281"/>
       <c r="B114" s="271" t="s">
         <v>145</v>
@@ -12886,7 +12872,7 @@
         <v>1221334.9700000002</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="281" t="s">
         <v>195</v>
       </c>
@@ -12908,7 +12894,7 @@
         <v>90879464.680000007</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="281" t="s">
         <v>203</v>
       </c>
@@ -12930,7 +12916,7 @@
         <v>10828622.959999999</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="281" t="s">
         <v>176</v>
       </c>
@@ -12952,7 +12938,7 @@
         <v>56096761.779999882</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="281" t="s">
         <v>204</v>
       </c>
@@ -12974,7 +12960,7 @@
         <v>42349125.859999932</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="281" t="s">
         <v>205</v>
       </c>
@@ -12996,7 +12982,7 @@
         <v>12460186.710000001</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="281" t="s">
         <v>253</v>
       </c>
@@ -13018,7 +13004,7 @@
         <v>1513833.15</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="281" t="s">
         <v>208</v>
       </c>
@@ -13040,7 +13026,7 @@
         <v>242485214.69000125</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="281" t="s">
         <v>210</v>
       </c>
@@ -13062,7 +13048,7 @@
         <v>130075043.88000013</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="281" t="s">
         <v>254</v>
       </c>
@@ -13084,7 +13070,7 @@
         <v>8317598.129999999</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="281" t="s">
         <v>215</v>
       </c>
@@ -13106,7 +13092,7 @@
         <v>19951807.690000013</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="281" t="s">
         <v>221</v>
       </c>
@@ -13128,7 +13114,7 @@
         <v>3514936.0200000005</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="281" t="s">
         <v>225</v>
       </c>
@@ -13150,7 +13136,7 @@
         <v>579441303.72000396</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="281" t="s">
         <v>226</v>
       </c>
@@ -13172,7 +13158,7 @@
         <v>170025769.98000044</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="281" t="s">
         <v>255</v>
       </c>
@@ -13194,7 +13180,7 @@
         <v>60282489.34999986</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="281" t="s">
         <v>228</v>
       </c>
@@ -13216,7 +13202,7 @@
         <v>103135696.96999992</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="281" t="s">
         <v>152</v>
       </c>
@@ -13238,7 +13224,7 @@
         <v>21394608.250000011</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="281" t="s">
         <v>256</v>
       </c>
@@ -13260,7 +13246,7 @@
         <v>20762694.490000002</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="281" t="s">
         <v>257</v>
       </c>
@@ -13282,7 +13268,7 @@
         <v>5977787.830000001</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="281" t="s">
         <v>229</v>
       </c>
@@ -13304,7 +13290,7 @@
         <v>181352079.10000029</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="281" t="s">
         <v>258</v>
       </c>
@@ -13326,7 +13312,7 @@
         <v>2442669.94</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="281" t="s">
         <v>149</v>
       </c>
@@ -13348,7 +13334,7 @@
         <v>25712040.959999997</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="281" t="s">
         <v>235</v>
       </c>
@@ -13370,7 +13356,7 @@
         <v>36875949.079999946</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="262" t="s">
         <v>236</v>
       </c>
@@ -13392,7 +13378,7 @@
         <v>1009222.1000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="281" t="s">
         <v>236</v>
       </c>
@@ -13414,7 +13400,7 @@
         <v>14656019.640000004</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="281" t="s">
         <v>171</v>
       </c>
@@ -13436,7 +13422,7 @@
         <v>7030017.2700000023</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="281" t="s">
         <v>239</v>
       </c>
@@ -13458,7 +13444,7 @@
         <v>348384027.26000243</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="281" t="s">
         <v>241</v>
       </c>
@@ -13480,7 +13466,7 @@
         <v>66260277.17999991</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="281" t="s">
         <v>174</v>
       </c>
@@ -13502,7 +13488,7 @@
         <v>339032466.54000002</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="262" t="s">
         <v>243</v>
       </c>
@@ -13524,7 +13510,7 @@
         <v>182776693.56999993</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="281" t="s">
         <v>245</v>
       </c>
@@ -13546,7 +13532,7 @@
         <v>614114.75</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="281" t="s">
         <v>246</v>
       </c>
@@ -13568,7 +13554,7 @@
         <v>92721808.929999992</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="281" t="s">
         <v>247</v>
       </c>
@@ -13590,7 +13576,7 @@
         <v>42349125.859999947</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="281" t="s">
         <v>164</v>
       </c>
@@ -13612,7 +13598,7 @@
         <v>139760675.00000012</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="281" t="s">
         <v>249</v>
       </c>
@@ -13634,7 +13620,7 @@
         <v>84690420.809999883</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="281" t="s">
         <v>259</v>
       </c>
@@ -13656,7 +13642,7 @@
         <v>7703483.379999999</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="281" t="s">
         <v>250</v>
       </c>
@@ -13678,7 +13664,7 @@
         <v>32976044.18999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="281" t="s">
         <v>196</v>
       </c>
@@ -13700,7 +13686,7 @@
         <v>4386979.9100000029</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="281" t="s">
         <v>197</v>
       </c>
@@ -13722,7 +13708,7 @@
         <v>108629205.9599967</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="281" t="s">
         <v>176</v>
       </c>
@@ -13744,7 +13730,7 @@
         <v>255081129.14003366</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="281" t="s">
         <v>208</v>
       </c>
@@ -13766,7 +13752,7 @@
         <v>1006884.1400000002</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="281" t="s">
         <v>214</v>
       </c>
@@ -13788,7 +13774,7 @@
         <v>1220654.8799999994</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="281" t="s">
         <v>219</v>
       </c>
@@ -13810,7 +13796,7 @@
         <v>238713553.10999355</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="281" t="s">
         <v>222</v>
       </c>
@@ -13832,7 +13818,7 @@
         <v>911585.5900000002</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="281" t="s">
         <v>225</v>
       </c>
@@ -13854,7 +13840,7 @@
         <v>2132240.4700000016</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="281" t="s">
         <v>261</v>
       </c>
@@ -13876,7 +13862,7 @@
         <v>1220654.8799999997</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="281" t="s">
         <v>144</v>
       </c>
@@ -13902,7 +13888,7 @@
       </c>
       <c r="Y160" s="218"/>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="281" t="s">
         <v>227</v>
       </c>
@@ -13924,7 +13910,7 @@
         <v>3592537.7499999967</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="281" t="s">
         <v>229</v>
       </c>
@@ -13946,7 +13932,7 @@
         <v>3020652.4200000013</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="281" t="s">
         <v>232</v>
       </c>
@@ -13968,7 +13954,7 @@
         <v>300455001.50000781</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="281" t="s">
         <v>233</v>
       </c>
@@ -13990,7 +13976,7 @@
         <v>1220654.8799999992</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="281" t="s">
         <v>171</v>
       </c>
@@ -14012,7 +13998,7 @@
         <v>399077386.25999945</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="281" t="s">
         <v>239</v>
       </c>
@@ -14034,7 +14020,7 @@
         <v>1006884.1399999999</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="281" t="s">
         <v>242</v>
       </c>
@@ -14056,7 +14042,7 @@
         <v>1006884.1400000001</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="281" t="s">
         <v>168</v>
       </c>
@@ -14088,7 +14074,7 @@
         <v>453601227.03999996</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="281" t="s">
         <v>246</v>
       </c>
@@ -14110,7 +14096,7 @@
         <v>1006884.1400000001</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="281" t="s">
         <v>164</v>
       </c>
@@ -14132,7 +14118,7 @@
         <v>9452726.7900000159</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="281" t="s">
         <v>248</v>
       </c>
@@ -14154,7 +14140,7 @@
         <v>1006884.1399999999</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="281" t="s">
         <v>185</v>
       </c>
@@ -14176,7 +14162,7 @@
         <v>22106208.609999988</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="281" t="s">
         <v>156</v>
       </c>
@@ -14198,7 +14184,7 @@
         <v>212080190.05000722</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="281" t="s">
         <v>173</v>
       </c>
@@ -14220,7 +14206,7 @@
         <v>33039185.340000134</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="313" t="s">
         <v>187</v>
       </c>
@@ -14242,7 +14228,7 @@
         <v>173307347.28000385</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="281" t="s">
         <v>165</v>
       </c>
@@ -14264,7 +14250,7 @@
         <v>249482271.56004351</v>
       </c>
     </row>
-    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="281" t="s">
         <v>191</v>
       </c>
@@ -14286,7 +14272,7 @@
         <v>69327183.080001146</v>
       </c>
     </row>
-    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="262" t="s">
         <v>144</v>
       </c>
@@ -14354,47 +14340,21 @@
         <v>18010939.100000001</v>
       </c>
     </row>
-    <row r="193" spans="33:37" ht="30" x14ac:dyDescent="0.25">
-      <c r="AG193" s="315" t="s">
-        <v>402</v>
-      </c>
-      <c r="AH193" s="315" t="s">
-        <v>404</v>
-      </c>
-      <c r="AI193" s="315" t="s">
-        <v>403</v>
-      </c>
-      <c r="AJ193" s="315" t="s">
-        <v>405</v>
-      </c>
-      <c r="AK193" s="315" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="194" spans="33:37" x14ac:dyDescent="0.25">
-      <c r="AG194">
-        <f>SUBTOTAL(109, J:K) / 1000000</f>
-        <v>1059.3830532599968</v>
-      </c>
-      <c r="AH194">
-        <f>SUBTOTAL(109, L:N) / 1000000</f>
-        <v>1200.2562837699995</v>
-      </c>
-      <c r="AI194">
-        <f>SUBTOTAL(109, O:T) / 1000000</f>
-        <v>8911.9068150793901</v>
-      </c>
-      <c r="AJ194">
-        <f>SUBTOTAL(109, U:AB) / 1000000</f>
-        <v>35925.660705731199</v>
-      </c>
-      <c r="AK194">
-        <f>SUBTOTAL(109, AC:AE) / 1000000</f>
-        <v>12374.010068559995</v>
-      </c>
+    <row r="193" spans="33:37" x14ac:dyDescent="0.25">
+      <c r="AG193" s="315"/>
+      <c r="AH193" s="315"/>
+      <c r="AI193" s="315"/>
+      <c r="AJ193" s="315"/>
+      <c r="AK193" s="315"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AE178" xr:uid="{BEBB7BC1-AB84-4C97-A7A0-E851126C3CB4}"/>
+  <autoFilter ref="A3:AE178" xr:uid="{BEBB7BC1-AB84-4C97-A7A0-E851126C3CB4}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="DDM CEN"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="5">
     <mergeCell ref="I1:S1"/>
     <mergeCell ref="T1:AD1"/>

--- a/Модель_покрытия_2026_для_заполнения_1.xlsx
+++ b/Модель_покрытия_2026_для_заполнения_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\world\Desktop\MARSIntMap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C739485-172E-443C-A7B4-309AB87C28BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EFDC73-5F24-4C51-BCED-9128FAC19339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{557A26C6-F21E-4F13-8F97-2AB80881C4B7}"/>
   </bookViews>
@@ -8668,7 +8668,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEBB7BC1-AB84-4C97-A7A0-E851126C3CB4}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AK193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8898,7 +8897,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="4" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="F4" s="263"/>
       <c r="G4" s="263"/>
       <c r="I4" s="264"/>
@@ -8940,7 +8939,7 @@
         <v>2220726460.6154871</v>
       </c>
     </row>
-    <row r="5" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="262" t="s">
         <v>149</v>
       </c>
@@ -8998,7 +8997,7 @@
         <v>271516.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="262" t="s">
         <v>152</v>
       </c>
@@ -9041,7 +9040,7 @@
       <c r="Y6" s="266"/>
       <c r="AE6" s="267"/>
     </row>
-    <row r="7" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="262" t="s">
         <v>149</v>
       </c>
@@ -9165,7 +9164,7 @@
         <v>21870426.049999997</v>
       </c>
     </row>
-    <row r="9" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="262" t="s">
         <v>160</v>
       </c>
@@ -9217,7 +9216,7 @@
         <v>1288855.8400000001</v>
       </c>
     </row>
-    <row r="10" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="262" t="s">
         <v>152</v>
       </c>
@@ -9262,7 +9261,7 @@
       <c r="AC10" s="267"/>
       <c r="AE10" s="267"/>
     </row>
-    <row r="11" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="262" t="s">
         <v>164</v>
       </c>
@@ -9312,7 +9311,7 @@
       </c>
       <c r="AE11" s="267"/>
     </row>
-    <row r="12" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="262" t="s">
         <v>165</v>
       </c>
@@ -9362,7 +9361,7 @@
       </c>
       <c r="AE12" s="267"/>
     </row>
-    <row r="13" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="262" t="s">
         <v>168</v>
       </c>
@@ -9407,7 +9406,7 @@
       </c>
       <c r="AE13" s="267"/>
     </row>
-    <row r="14" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="262" t="s">
         <v>168</v>
       </c>
@@ -9454,7 +9453,7 @@
       </c>
       <c r="AE14" s="267"/>
     </row>
-    <row r="15" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="262" t="s">
         <v>171</v>
       </c>
@@ -9504,7 +9503,7 @@
       </c>
       <c r="AE15" s="267"/>
     </row>
-    <row r="16" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="262" t="s">
         <v>173</v>
       </c>
@@ -9551,7 +9550,7 @@
       <c r="AC16" s="267"/>
       <c r="AE16" s="267"/>
     </row>
-    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="262" t="s">
         <v>174</v>
       </c>
@@ -9600,7 +9599,7 @@
       </c>
       <c r="AE17" s="267"/>
     </row>
-    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="262" t="s">
         <v>160</v>
       </c>
@@ -9647,7 +9646,7 @@
       <c r="AC18" s="267"/>
       <c r="AE18" s="267"/>
     </row>
-    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="262" t="s">
         <v>176</v>
       </c>
@@ -9697,7 +9696,7 @@
       </c>
       <c r="AE19" s="267"/>
     </row>
-    <row r="20" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="262" t="s">
         <v>149</v>
       </c>
@@ -9768,7 +9767,7 @@
         <v>1997857.99</v>
       </c>
     </row>
-    <row r="21" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" s="262" t="s">
         <v>176</v>
       </c>
@@ -9824,7 +9823,7 @@
         <v>16290350.629999997</v>
       </c>
     </row>
-    <row r="22" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="262" t="s">
         <v>171</v>
       </c>
@@ -9915,7 +9914,7 @@
       <c r="X23" s="218"/>
       <c r="AE23" s="267"/>
     </row>
-    <row r="24" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="262" t="s">
         <v>174</v>
       </c>
@@ -9964,7 +9963,7 @@
         <v>6582960</v>
       </c>
     </row>
-    <row r="25" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="262" t="s">
         <v>174</v>
       </c>
@@ -9999,7 +9998,7 @@
         <v>293012.60000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="262" t="s">
         <v>168</v>
       </c>
@@ -10045,7 +10044,7 @@
         <v>63038286.849999949</v>
       </c>
     </row>
-    <row r="27" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="262" t="s">
         <v>168</v>
       </c>
@@ -10145,7 +10144,7 @@
       <c r="W28" s="267"/>
       <c r="AE28" s="267"/>
     </row>
-    <row r="29" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="262" t="s">
         <v>168</v>
       </c>
@@ -10225,7 +10224,7 @@
       <c r="W30" s="267"/>
       <c r="AE30" s="267"/>
     </row>
-    <row r="31" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="262" t="s">
         <v>164</v>
       </c>
@@ -10266,7 +10265,7 @@
       <c r="W31" s="267"/>
       <c r="AE31" s="267"/>
     </row>
-    <row r="32" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="262" t="s">
         <v>164</v>
       </c>
@@ -10394,7 +10393,7 @@
       <c r="S34" s="265"/>
       <c r="AE34" s="267"/>
     </row>
-    <row r="35" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="262" t="s">
         <v>156</v>
       </c>
@@ -10427,7 +10426,7 @@
       <c r="S35" s="265"/>
       <c r="AE35" s="267"/>
     </row>
-    <row r="36" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" s="262" t="s">
         <v>173</v>
       </c>
@@ -10478,7 +10477,7 @@
         <v>669466</v>
       </c>
     </row>
-    <row r="37" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" s="262" t="s">
         <v>173</v>
       </c>
@@ -10582,7 +10581,7 @@
       </c>
       <c r="AE38" s="267"/>
     </row>
-    <row r="39" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39" s="262" t="s">
         <v>165</v>
       </c>
@@ -10615,7 +10614,7 @@
       <c r="S39" s="265"/>
       <c r="AE39" s="267"/>
     </row>
-    <row r="40" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40" s="262" t="s">
         <v>165</v>
       </c>
@@ -10711,7 +10710,7 @@
       <c r="S41" s="265"/>
       <c r="AE41" s="267"/>
     </row>
-    <row r="42" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42" s="262" t="s">
         <v>165</v>
       </c>
@@ -10810,7 +10809,7 @@
         <v>3859752.72</v>
       </c>
     </row>
-    <row r="44" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44" s="262" t="s">
         <v>192</v>
       </c>
@@ -10833,7 +10832,7 @@
       </c>
       <c r="J44" s="267"/>
     </row>
-    <row r="45" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A45" s="262" t="s">
         <v>192</v>
       </c>
@@ -10876,7 +10875,7 @@
       <c r="AC45" s="272"/>
       <c r="AD45" s="272"/>
     </row>
-    <row r="46" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A46" s="262" t="s">
         <v>192</v>
       </c>
@@ -10898,7 +10897,7 @@
         <v>228590.15</v>
       </c>
     </row>
-    <row r="47" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A47" s="262" t="s">
         <v>192</v>
       </c>
@@ -10921,7 +10920,7 @@
       </c>
       <c r="X47" s="273"/>
     </row>
-    <row r="48" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="262" t="s">
         <v>195</v>
       </c>
@@ -10943,7 +10942,7 @@
         <v>44163988.919999994</v>
       </c>
     </row>
-    <row r="49" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="281" t="s">
         <v>195</v>
       </c>
@@ -10983,7 +10982,7 @@
       <c r="AC49" s="274"/>
       <c r="AD49" s="274"/>
     </row>
-    <row r="50" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="262" t="s">
         <v>196</v>
       </c>
@@ -11023,7 +11022,7 @@
       <c r="AC50" s="265"/>
       <c r="AD50" s="265"/>
     </row>
-    <row r="51" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="281" t="s">
         <v>196</v>
       </c>
@@ -11066,7 +11065,7 @@
       <c r="AC51" s="265"/>
       <c r="AD51" s="265"/>
     </row>
-    <row r="52" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="262" t="s">
         <v>197</v>
       </c>
@@ -11109,7 +11108,7 @@
       <c r="AC52" s="265"/>
       <c r="AD52" s="265"/>
     </row>
-    <row r="53" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="281" t="s">
         <v>197</v>
       </c>
@@ -11152,7 +11151,7 @@
       <c r="AC53" s="265"/>
       <c r="AD53" s="265"/>
     </row>
-    <row r="54" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="281" t="s">
         <v>198</v>
       </c>
@@ -11195,7 +11194,7 @@
       <c r="AC54" s="265"/>
       <c r="AD54" s="265"/>
     </row>
-    <row r="55" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="262" t="s">
         <v>200</v>
       </c>
@@ -11238,7 +11237,7 @@
       <c r="AC55" s="265"/>
       <c r="AD55" s="265"/>
     </row>
-    <row r="56" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="281" t="s">
         <v>200</v>
       </c>
@@ -11281,7 +11280,7 @@
       <c r="AC56" s="265"/>
       <c r="AD56" s="265"/>
     </row>
-    <row r="57" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="281" t="s">
         <v>203</v>
       </c>
@@ -11324,7 +11323,7 @@
       <c r="AC57" s="265"/>
       <c r="AD57" s="265"/>
     </row>
-    <row r="58" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="281" t="s">
         <v>176</v>
       </c>
@@ -11367,7 +11366,7 @@
       <c r="AC58" s="265"/>
       <c r="AD58" s="265"/>
     </row>
-    <row r="59" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="281" t="s">
         <v>204</v>
       </c>
@@ -11410,7 +11409,7 @@
       <c r="AC59" s="265"/>
       <c r="AD59" s="265"/>
     </row>
-    <row r="60" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="281" t="s">
         <v>205</v>
       </c>
@@ -11453,7 +11452,7 @@
       <c r="AC60" s="265"/>
       <c r="AD60" s="265"/>
     </row>
-    <row r="61" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="281" t="s">
         <v>206</v>
       </c>
@@ -11496,7 +11495,7 @@
       <c r="AC61" s="265"/>
       <c r="AD61" s="265"/>
     </row>
-    <row r="62" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="281" t="s">
         <v>208</v>
       </c>
@@ -11539,7 +11538,7 @@
       <c r="AC62" s="265"/>
       <c r="AD62" s="265"/>
     </row>
-    <row r="63" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="262" t="s">
         <v>209</v>
       </c>
@@ -11582,7 +11581,7 @@
       <c r="AC63" s="265"/>
       <c r="AD63" s="265"/>
     </row>
-    <row r="64" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="281" t="s">
         <v>209</v>
       </c>
@@ -11625,7 +11624,7 @@
       <c r="AC64" s="265"/>
       <c r="AD64" s="265"/>
     </row>
-    <row r="65" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A65" s="281" t="s">
         <v>210</v>
       </c>
@@ -11668,7 +11667,7 @@
       <c r="AC65" s="265"/>
       <c r="AD65" s="265"/>
     </row>
-    <row r="66" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A66" s="313" t="s">
         <v>211</v>
       </c>
@@ -11711,7 +11710,7 @@
       <c r="AC66" s="265"/>
       <c r="AD66" s="265"/>
     </row>
-    <row r="67" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A67" s="281" t="s">
         <v>212</v>
       </c>
@@ -11756,7 +11755,7 @@
       <c r="AD67" s="276"/>
       <c r="AE67" s="276"/>
     </row>
-    <row r="68" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A68" s="281" t="s">
         <v>214</v>
       </c>
@@ -11799,7 +11798,7 @@
       <c r="AC68" s="265"/>
       <c r="AD68" s="265"/>
     </row>
-    <row r="69" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A69" s="281" t="s">
         <v>215</v>
       </c>
@@ -11842,7 +11841,7 @@
       <c r="AC69" s="265"/>
       <c r="AD69" s="265"/>
     </row>
-    <row r="70" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A70" s="281" t="s">
         <v>216</v>
       </c>
@@ -11885,7 +11884,7 @@
       <c r="AC70" s="265"/>
       <c r="AD70" s="265"/>
     </row>
-    <row r="71" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A71" s="281" t="s">
         <v>217</v>
       </c>
@@ -11907,7 +11906,7 @@
         <v>3642683.080000001</v>
       </c>
     </row>
-    <row r="72" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A72" s="313" t="s">
         <v>219</v>
       </c>
@@ -11929,7 +11928,7 @@
         <v>16476732.709999997</v>
       </c>
     </row>
-    <row r="73" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A73" s="281" t="s">
         <v>221</v>
       </c>
@@ -11951,7 +11950,7 @@
         <v>1067159.2200000002</v>
       </c>
     </row>
-    <row r="74" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A74" s="281" t="s">
         <v>222</v>
       </c>
@@ -11994,7 +11993,7 @@
       <c r="AC74" s="272"/>
       <c r="AD74" s="272"/>
     </row>
-    <row r="75" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A75" s="281" t="s">
         <v>224</v>
       </c>
@@ -12016,7 +12015,7 @@
         <v>217936.43</v>
       </c>
     </row>
-    <row r="76" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A76" s="262" t="s">
         <v>225</v>
       </c>
@@ -12038,7 +12037,7 @@
         <v>18206006.04000001</v>
       </c>
     </row>
-    <row r="77" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A77" s="281" t="s">
         <v>225</v>
       </c>
@@ -12060,7 +12059,7 @@
         <v>22305574.450000003</v>
       </c>
     </row>
-    <row r="78" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A78" s="281" t="s">
         <v>226</v>
       </c>
@@ -12082,7 +12081,7 @@
         <v>148303293.16999984</v>
       </c>
     </row>
-    <row r="79" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A79" s="281" t="s">
         <v>144</v>
       </c>
@@ -12104,7 +12103,7 @@
         <v>18010939.100000005</v>
       </c>
     </row>
-    <row r="80" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A80" s="281" t="s">
         <v>227</v>
       </c>
@@ -12126,7 +12125,7 @@
         <v>8843623.5500000007</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="281" t="s">
         <v>228</v>
       </c>
@@ -12148,7 +12147,7 @@
         <v>4388912.41</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="281" t="s">
         <v>229</v>
       </c>
@@ -12170,7 +12169,7 @@
         <v>16865038.440000001</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="281" t="s">
         <v>230</v>
       </c>
@@ -12192,7 +12191,7 @@
         <v>2126298.59</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="281" t="s">
         <v>231</v>
       </c>
@@ -12214,7 +12213,7 @@
         <v>2711752.3</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="262" t="s">
         <v>232</v>
       </c>
@@ -12236,7 +12235,7 @@
         <v>6187042.1399999997</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="281" t="s">
         <v>232</v>
       </c>
@@ -12258,7 +12257,7 @@
         <v>6168560.4500000011</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="281" t="s">
         <v>233</v>
       </c>
@@ -12280,7 +12279,7 @@
         <v>13379034.709999999</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="281" t="s">
         <v>149</v>
       </c>
@@ -12302,7 +12301,7 @@
         <v>2367448.2399999998</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="281" t="s">
         <v>235</v>
       </c>
@@ -12324,7 +12323,7 @@
         <v>66978.100000000006</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="281" t="s">
         <v>236</v>
       </c>
@@ -12346,7 +12345,7 @@
         <v>1620898.1300000001</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="281" t="s">
         <v>171</v>
       </c>
@@ -12368,7 +12367,7 @@
         <v>36021878.200000018</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="281" t="s">
         <v>237</v>
       </c>
@@ -12390,7 +12389,7 @@
         <v>132631.12</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="281" t="s">
         <v>238</v>
       </c>
@@ -12412,7 +12411,7 @@
         <v>7241718.1199999992</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="281" t="s">
         <v>239</v>
       </c>
@@ -12434,7 +12433,7 @@
         <v>2537846.2700000005</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="281" t="s">
         <v>241</v>
       </c>
@@ -12456,7 +12455,7 @@
         <v>1761030.05</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="281" t="s">
         <v>174</v>
       </c>
@@ -12478,7 +12477,7 @@
         <v>6875972.790000001</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="281" t="s">
         <v>242</v>
       </c>
@@ -12500,7 +12499,7 @@
         <v>166482.5</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="281" t="s">
         <v>243</v>
       </c>
@@ -12522,7 +12521,7 @@
         <v>923748.45000000019</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="281" t="s">
         <v>244</v>
       </c>
@@ -12544,7 +12543,7 @@
         <v>915171.79</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="281" t="s">
         <v>245</v>
       </c>
@@ -12566,7 +12565,7 @@
         <v>24173379.469999999</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="281" t="s">
         <v>246</v>
       </c>
@@ -12588,7 +12587,7 @@
         <v>3460921.04</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="281" t="s">
         <v>247</v>
       </c>
@@ -12610,7 +12609,7 @@
         <v>3728265.5200000005</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="281" t="s">
         <v>164</v>
       </c>
@@ -12632,7 +12631,7 @@
         <v>292274.43</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="281" t="s">
         <v>248</v>
       </c>
@@ -12654,7 +12653,7 @@
         <v>372200.5</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="281" t="s">
         <v>185</v>
       </c>
@@ -12676,7 +12675,7 @@
         <v>5559329.3000000007</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="281" t="s">
         <v>249</v>
       </c>
@@ -12698,7 +12697,7 @@
         <v>1871079.9999999998</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="281" t="s">
         <v>156</v>
       </c>
@@ -12720,7 +12719,7 @@
         <v>21870426.050000016</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="281" t="s">
         <v>173</v>
       </c>
@@ -12742,7 +12741,7 @@
         <v>669465.87</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="281" t="s">
         <v>165</v>
       </c>
@@ -12764,7 +12763,7 @@
         <v>59178799.899999708</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="313" t="s">
         <v>250</v>
       </c>
@@ -12786,7 +12785,7 @@
         <v>221696.62000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="281" t="s">
         <v>191</v>
       </c>
@@ -12808,7 +12807,7 @@
         <v>3859752.7199999997</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="281" t="s">
         <v>251</v>
       </c>
@@ -12830,7 +12829,7 @@
         <v>1319912.0300000003</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="262" t="s">
         <v>252</v>
       </c>
@@ -12852,7 +12851,7 @@
         <v>18991406.05999998</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="281"/>
       <c r="B114" s="271" t="s">
         <v>145</v>
@@ -12872,7 +12871,7 @@
         <v>1221334.9700000002</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="281" t="s">
         <v>195</v>
       </c>
@@ -12894,7 +12893,7 @@
         <v>90879464.680000007</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="281" t="s">
         <v>203</v>
       </c>
@@ -12916,7 +12915,7 @@
         <v>10828622.959999999</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="281" t="s">
         <v>176</v>
       </c>
@@ -12938,7 +12937,7 @@
         <v>56096761.779999882</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="281" t="s">
         <v>204</v>
       </c>
@@ -12960,7 +12959,7 @@
         <v>42349125.859999932</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="281" t="s">
         <v>205</v>
       </c>
@@ -12982,7 +12981,7 @@
         <v>12460186.710000001</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="281" t="s">
         <v>253</v>
       </c>
@@ -13004,7 +13003,7 @@
         <v>1513833.15</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="281" t="s">
         <v>208</v>
       </c>
@@ -13026,7 +13025,7 @@
         <v>242485214.69000125</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="281" t="s">
         <v>210</v>
       </c>
@@ -13048,7 +13047,7 @@
         <v>130075043.88000013</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="281" t="s">
         <v>254</v>
       </c>
@@ -13070,7 +13069,7 @@
         <v>8317598.129999999</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="281" t="s">
         <v>215</v>
       </c>
@@ -13092,7 +13091,7 @@
         <v>19951807.690000013</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="281" t="s">
         <v>221</v>
       </c>
@@ -13114,7 +13113,7 @@
         <v>3514936.0200000005</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="281" t="s">
         <v>225</v>
       </c>
@@ -13136,7 +13135,7 @@
         <v>579441303.72000396</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="281" t="s">
         <v>226</v>
       </c>
@@ -13158,7 +13157,7 @@
         <v>170025769.98000044</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="281" t="s">
         <v>255</v>
       </c>
@@ -13180,7 +13179,7 @@
         <v>60282489.34999986</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="281" t="s">
         <v>228</v>
       </c>
@@ -13202,7 +13201,7 @@
         <v>103135696.96999992</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="281" t="s">
         <v>152</v>
       </c>
@@ -13224,7 +13223,7 @@
         <v>21394608.250000011</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="281" t="s">
         <v>256</v>
       </c>
@@ -13246,7 +13245,7 @@
         <v>20762694.490000002</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="281" t="s">
         <v>257</v>
       </c>
@@ -13268,7 +13267,7 @@
         <v>5977787.830000001</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="281" t="s">
         <v>229</v>
       </c>
@@ -13290,7 +13289,7 @@
         <v>181352079.10000029</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="281" t="s">
         <v>258</v>
       </c>
@@ -13312,7 +13311,7 @@
         <v>2442669.94</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="281" t="s">
         <v>149</v>
       </c>
@@ -13334,7 +13333,7 @@
         <v>25712040.959999997</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="281" t="s">
         <v>235</v>
       </c>
@@ -13356,7 +13355,7 @@
         <v>36875949.079999946</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="262" t="s">
         <v>236</v>
       </c>
@@ -13378,7 +13377,7 @@
         <v>1009222.1000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="281" t="s">
         <v>236</v>
       </c>
@@ -13400,7 +13399,7 @@
         <v>14656019.640000004</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="281" t="s">
         <v>171</v>
       </c>
@@ -13422,7 +13421,7 @@
         <v>7030017.2700000023</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="281" t="s">
         <v>239</v>
       </c>
@@ -13444,7 +13443,7 @@
         <v>348384027.26000243</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="281" t="s">
         <v>241</v>
       </c>
@@ -13466,7 +13465,7 @@
         <v>66260277.17999991</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="281" t="s">
         <v>174</v>
       </c>
@@ -13488,7 +13487,7 @@
         <v>339032466.54000002</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="262" t="s">
         <v>243</v>
       </c>
@@ -13510,7 +13509,7 @@
         <v>182776693.56999993</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="281" t="s">
         <v>245</v>
       </c>
@@ -13532,7 +13531,7 @@
         <v>614114.75</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="281" t="s">
         <v>246</v>
       </c>
@@ -13554,7 +13553,7 @@
         <v>92721808.929999992</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="281" t="s">
         <v>247</v>
       </c>
@@ -13576,7 +13575,7 @@
         <v>42349125.859999947</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="281" t="s">
         <v>164</v>
       </c>
@@ -13598,7 +13597,7 @@
         <v>139760675.00000012</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="281" t="s">
         <v>249</v>
       </c>
@@ -13620,7 +13619,7 @@
         <v>84690420.809999883</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="281" t="s">
         <v>259</v>
       </c>
@@ -13642,7 +13641,7 @@
         <v>7703483.379999999</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="281" t="s">
         <v>250</v>
       </c>
@@ -13664,7 +13663,7 @@
         <v>32976044.18999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="281" t="s">
         <v>196</v>
       </c>
@@ -13686,7 +13685,7 @@
         <v>4386979.9100000029</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="281" t="s">
         <v>197</v>
       </c>
@@ -13708,7 +13707,7 @@
         <v>108629205.9599967</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="281" t="s">
         <v>176</v>
       </c>
@@ -13730,7 +13729,7 @@
         <v>255081129.14003366</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="281" t="s">
         <v>208</v>
       </c>
@@ -13752,7 +13751,7 @@
         <v>1006884.1400000002</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="281" t="s">
         <v>214</v>
       </c>
@@ -13774,7 +13773,7 @@
         <v>1220654.8799999994</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" s="281" t="s">
         <v>219</v>
       </c>
@@ -13796,7 +13795,7 @@
         <v>238713553.10999355</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" s="281" t="s">
         <v>222</v>
       </c>
@@ -13818,7 +13817,7 @@
         <v>911585.5900000002</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="281" t="s">
         <v>225</v>
       </c>
@@ -13840,7 +13839,7 @@
         <v>2132240.4700000016</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="281" t="s">
         <v>261</v>
       </c>
@@ -13862,7 +13861,7 @@
         <v>1220654.8799999997</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="281" t="s">
         <v>144</v>
       </c>
@@ -13888,7 +13887,7 @@
       </c>
       <c r="Y160" s="218"/>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" s="281" t="s">
         <v>227</v>
       </c>
@@ -13910,7 +13909,7 @@
         <v>3592537.7499999967</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" s="281" t="s">
         <v>229</v>
       </c>
@@ -13932,7 +13931,7 @@
         <v>3020652.4200000013</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" s="281" t="s">
         <v>232</v>
       </c>
@@ -13954,7 +13953,7 @@
         <v>300455001.50000781</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" s="281" t="s">
         <v>233</v>
       </c>
@@ -13976,7 +13975,7 @@
         <v>1220654.8799999992</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" s="281" t="s">
         <v>171</v>
       </c>
@@ -13998,7 +13997,7 @@
         <v>399077386.25999945</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" s="281" t="s">
         <v>239</v>
       </c>
@@ -14020,7 +14019,7 @@
         <v>1006884.1399999999</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" s="281" t="s">
         <v>242</v>
       </c>
@@ -14042,7 +14041,7 @@
         <v>1006884.1400000001</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="281" t="s">
         <v>168</v>
       </c>
@@ -14074,7 +14073,7 @@
         <v>453601227.03999996</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" s="281" t="s">
         <v>246</v>
       </c>
@@ -14096,7 +14095,7 @@
         <v>1006884.1400000001</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" s="281" t="s">
         <v>164</v>
       </c>
@@ -14118,7 +14117,7 @@
         <v>9452726.7900000159</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" s="281" t="s">
         <v>248</v>
       </c>
@@ -14140,7 +14139,7 @@
         <v>1006884.1399999999</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" s="281" t="s">
         <v>185</v>
       </c>
@@ -14162,7 +14161,7 @@
         <v>22106208.609999988</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" s="281" t="s">
         <v>156</v>
       </c>
@@ -14184,7 +14183,7 @@
         <v>212080190.05000722</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" s="281" t="s">
         <v>173</v>
       </c>
@@ -14206,7 +14205,7 @@
         <v>33039185.340000134</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" s="313" t="s">
         <v>187</v>
       </c>
@@ -14228,7 +14227,7 @@
         <v>173307347.28000385</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" s="281" t="s">
         <v>165</v>
       </c>
@@ -14250,7 +14249,7 @@
         <v>249482271.56004351</v>
       </c>
     </row>
-    <row r="177" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A177" s="281" t="s">
         <v>191</v>
       </c>
@@ -14272,7 +14271,7 @@
         <v>69327183.080001146</v>
       </c>
     </row>
-    <row r="178" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A178" s="262" t="s">
         <v>144</v>
       </c>
@@ -14348,13 +14347,7 @@
       <c r="AK193" s="315"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AE178" xr:uid="{BEBB7BC1-AB84-4C97-A7A0-E851126C3CB4}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="DDM CEN"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AE178" xr:uid="{BEBB7BC1-AB84-4C97-A7A0-E851126C3CB4}"/>
   <mergeCells count="5">
     <mergeCell ref="I1:S1"/>
     <mergeCell ref="T1:AD1"/>
